--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/abr-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2427-295-CM26</t>
+          <t>3621-125-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.200-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE CABILDO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13205.43</v>
+        <v>17387.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3621-125-CM26</t>
+          <t>2427-295-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.050.200-3</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABILDO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>17387.27</v>
+        <v>13205.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2403-42-CM26</t>
+          <t>1048-124-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,57 +1505,53 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>559476.12</v>
+        <v>41279.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1048-124-CM26</t>
+          <t>1057508-1515-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1580,27 +1576,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.607.000-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>SERVICIO DE SALUD NUBLE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>41279.32</v>
+        <v>1999.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057508-1515-CM26</t>
+          <t>1002584-128-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1641,43 +1637,47 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.607.000-2</t>
+          <t>65.154.016-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE</t>
+          <t>DIRECCION DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>76.334.381-2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1999.2</v>
+        <v>114494.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1002584-128-CM26</t>
+          <t>1300026-9-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.154.016-k</t>
+          <t>65.497.180-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION PUBLICA</t>
+          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,32 +1717,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>114494.66</v>
+        <v>1774.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1300026-9-CM26</t>
+          <t>1592-28-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,7 +1753,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1767,12 +1763,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>65.497.180-3</t>
+          <t>61.503.000-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LA COMUNA DE LA GRANJA</t>
+          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1782,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.334.381-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1797,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1774.05</v>
+        <v>16439.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1592-28-CM26</t>
+          <t>1592-29-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1843,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TICHILE  REVENTA  DE SOFTWARE Y HARDWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.334.381-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1858,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>16439.18</v>
+        <v>12272.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1592-29-CM26</t>
+          <t>3654-91-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1884,17 +1880,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.503.000-7</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVISION SOCIAL</t>
+          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1904,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1919,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>12272.14</v>
+        <v>18147.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2407-214-CM26</t>
+          <t>2385-237-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1945,32 +1941,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cancelada por Comprador</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1980,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3039.34</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3654-91-CM26</t>
+          <t>3756-258-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2011,17 +2007,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2041,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>18147.5</v>
+        <v>11614.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2385-237-CM26</t>
+          <t>1276532-11-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2062,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2072,27 +2068,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Administración Central</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2102,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1479.41</v>
+        <v>10119.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3756-258-CM26</t>
+          <t>975-102-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2123,37 +2119,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2163,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>11614.4</v>
+        <v>4470.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1276532-11-CM26</t>
+          <t>975-101-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2184,37 +2180,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Administración Central</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2224,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>10119.15</v>
+        <v>224533.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>975-102-CM26</t>
+          <t>3497-158-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2250,32 +2246,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2285,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4470.83</v>
+        <v>7500.11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>975-101-CM26</t>
+          <t>926853-9-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2311,32 +2307,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2346,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>224533.9</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3497-158-CM26</t>
+          <t>3874-67-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2377,27 +2373,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2407,13 +2403,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7500.11</v>
+        <v>2523.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>926853-9-CM26</t>
+          <t>3904-282-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2428,27 +2424,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>69.141.200-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>I MUNICIPALIDAD DE BULNES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2468,13 +2464,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>845.38</v>
+        <v>3170.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3874-67-CM26</t>
+          <t>1426104-35-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2489,7 +2485,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2499,27 +2495,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>Site Chile Sociedad Anónima</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.988.790-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2523.99</v>
+        <v>850.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3904-282-CM26</t>
+          <t>1216088-95-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2550,37 +2546,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.141.200-8</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BULNES</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3170.16</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1426104-35-CM26</t>
+          <t>542429-19-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2611,7 +2607,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,27 +2617,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Site Chile Sociedad Anónima</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.988.790-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>850.85</v>
+        <v>7890.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1216088-95-CM26</t>
+          <t>4294-60-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2682,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>65.077.010-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>845.38</v>
+        <v>14794.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>542429-19-CM26</t>
+          <t>3712-291-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2733,7 +2729,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,17 +2739,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2773,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>7890.56</v>
+        <v>11718.64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4294-60-CM26</t>
+          <t>4454-332-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2794,37 +2790,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>65.077.010-2</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2834,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14794.08</v>
+        <v>2307.83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3712-291-CM26</t>
+          <t>539119-1297-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2865,17 +2861,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2895,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>11718.64</v>
+        <v>845.38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4454-332-CM26</t>
+          <t>1151575-9-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2916,7 +2912,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,27 +2922,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>65.195.573-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>XMS TECHNOLOGIES S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.083.145-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2307.83</v>
+        <v>3077.82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>539119-1297-CM26</t>
+          <t>3708-146-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2977,7 +2973,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2987,27 +2983,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NETSUS SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>845.38</v>
+        <v>32092.52</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1151575-9-CM26</t>
+          <t>4134-274-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3038,37 +3034,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.195.573-4</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ATACAMA</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>XMS TECHNOLOGIES S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.083.145-k</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3077.82</v>
+        <v>22175.65</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3708-146-CM26</t>
+          <t>1057473-140-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3104,32 +3100,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.999.030-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>SAMU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>32092.52</v>
+        <v>70764.53999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4134-274-CM26</t>
+          <t>1415862-20-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3170,43 +3166,47 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>Instituto de Seguridad Laboral</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>22175.65</v>
+        <v>216159.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057473-140-CM26</t>
+          <t>2548-229-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3231,27 +3231,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.999.030-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>70764.53999999999</v>
+        <v>9721.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1415862-20-CM26</t>
+          <t>2429-405-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3292,47 +3292,43 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.770.640-k</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>216159.216</v>
+        <v>5273.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2548-229-CM26</t>
+          <t>539119-1346-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3347,37 +3343,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.505.720-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>Carabineros de Chile - Dirección de Bienestar</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3383,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9721.82</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2429-405-CM26</t>
+          <t>3884-203-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3408,7 +3404,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3418,27 +3414,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3448,13 +3444,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5273.5</v>
+        <v>11805.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>539119-1346-CM26</t>
+          <t>1288-250-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3469,22 +3465,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.505.720-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3494,12 +3490,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3509,13 +3505,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1479.41</v>
+        <v>1076.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3884-203-CM26</t>
+          <t>3517-60-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3535,32 +3531,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,13 +3566,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11805.99</v>
+        <v>5588.26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1288-250-CM26</t>
+          <t>2713-473-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3591,27 +3587,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3631,13 +3627,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1076.99</v>
+        <v>44351.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3337-95-CM26</t>
+          <t>948354-703-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3652,22 +3648,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>No aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.101.032-K</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIVISION DE SALUD</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,12 +3673,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3692,13 +3688,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>827.03</v>
+        <v>21134.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3517-60-CM26</t>
+          <t>610-21-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3713,37 +3709,37 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.707.000-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>Comisión Nacional de Energía</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3749,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5588.26</v>
+        <v>2941.38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2713-473-CM26</t>
+          <t>2580-175-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,7 +3770,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3784,27 +3780,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,189 +3810,6 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>44351.3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>948354-703-CM26</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>61.513.003-6</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>21134.4</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>610-21-CM26</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>61.707.000-6</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Comisión Nacional de Energía</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>2941.38</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2580-175-CM26</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>abr-2026</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>60.818.000-1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Superintendencia de Pensiones</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="n">
         <v>15856.75</v>
       </c>
     </row>
